--- a/SGC-CKN/Excel/e735cd7a-1084-4898-afb7-9900d9305cdb_Lô_CT-02_P1-7_D800_02-04-2026.xlsx
+++ b/SGC-CKN/Excel/e735cd7a-1084-4898-afb7-9900d9305cdb_Lô_CT-02_P1-7_D800_02-04-2026.xlsx
@@ -125,7 +125,7 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">23:55
+    <t xml:space="preserve">23:35
 01/04/2026</t>
   </si>
   <si>
@@ -346,12 +346,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFECACA"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFFECACA"/>
       </patternFill>
     </fill>
     <fill>
@@ -516,17 +516,17 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1235,50 +1235,50 @@
         <v>-8.5</v>
       </c>
       <c r="H13" s="12">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="I13" s="12">
         <v>3.5</v>
       </c>
-      <c r="J13" s="8">
-        <v>4.2</v>
+      <c r="J13" s="15">
+        <v>7</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="16">
         <v>-8.5</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="16">
         <v>-17.3</v>
       </c>
-      <c r="H14" s="15">
-        <v>0.33</v>
-      </c>
-      <c r="I14" s="15">
+      <c r="H14" s="16">
+        <v>0.67</v>
+      </c>
+      <c r="I14" s="16">
         <v>8.8</v>
       </c>
-      <c r="J14" s="18">
-        <v>26.4</v>
-      </c>
-      <c r="K14" s="16" t="s">
+      <c r="J14" s="15">
+        <v>13.2</v>
+      </c>
+      <c r="K14" s="17" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       <c r="I15" s="19">
         <v>5.4</v>
       </c>
-      <c r="J15" s="18">
+      <c r="J15" s="15">
         <v>5.4</v>
       </c>
       <c r="K15" s="20" t="s">
@@ -1372,16 +1372,16 @@
         <v>-26.5</v>
       </c>
       <c r="G17" s="25">
-        <v>-40.4</v>
+        <v>-40</v>
       </c>
       <c r="H17" s="25">
         <v>1.5</v>
       </c>
       <c r="I17" s="25">
-        <v>13.9</v>
-      </c>
-      <c r="J17" s="18">
-        <v>9.27</v>
+        <v>13.5</v>
+      </c>
+      <c r="J17" s="15">
+        <v>9</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1404,7 +1404,7 @@
         <v>51</v>
       </c>
       <c r="F18" s="28">
-        <v>-40.4</v>
+        <v>-40</v>
       </c>
       <c r="G18" s="28">
         <v>-44.55</v>
@@ -1413,10 +1413,10 @@
         <v>4.62</v>
       </c>
       <c r="I18" s="28">
-        <v>4.15</v>
+        <v>4.55</v>
       </c>
       <c r="J18" s="31">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1635,42 +1635,42 @@
         <v>-8.5</v>
       </c>
       <c r="G4" s="12">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="H4" s="12">
         <v>3.5</v>
       </c>
-      <c r="I4" s="8">
-        <v>4.2</v>
+      <c r="I4" s="15">
+        <v>7</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+      <c r="A5" s="16">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="16">
         <v>1</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="16">
         <v>-8.5</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="16">
         <v>-17.3</v>
       </c>
-      <c r="G5" s="15">
-        <v>0.33</v>
-      </c>
-      <c r="H5" s="15">
+      <c r="G5" s="16">
+        <v>0.67</v>
+      </c>
+      <c r="H5" s="16">
         <v>8.8</v>
       </c>
-      <c r="I5" s="18">
-        <v>26.4</v>
+      <c r="I5" s="15">
+        <v>13.2</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1698,7 +1698,7 @@
       <c r="H6" s="19">
         <v>5.4</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="15">
         <v>5.4</v>
       </c>
     </row>
@@ -1748,16 +1748,16 @@
         <v>-26.5</v>
       </c>
       <c r="F8" s="25">
-        <v>-40.4</v>
+        <v>-40</v>
       </c>
       <c r="G8" s="25">
         <v>1.5</v>
       </c>
       <c r="H8" s="25">
-        <v>13.9</v>
-      </c>
-      <c r="I8" s="18">
-        <v>9.27</v>
+        <v>13.5</v>
+      </c>
+      <c r="I8" s="15">
+        <v>9</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1774,7 +1774,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-40.4</v>
+        <v>-40</v>
       </c>
       <c r="F9" s="28">
         <v>-44.55</v>
@@ -1783,10 +1783,10 @@
         <v>4.62</v>
       </c>
       <c r="H9" s="28">
-        <v>4.15</v>
+        <v>4.55</v>
       </c>
       <c r="I9" s="31">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
